--- a/data/reports/2024-04-08/2024-04-08_duplicates.xlsx
+++ b/data/reports/2024-04-08/2024-04-08_duplicates.xlsx
@@ -187,7 +187,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005813</t>
+    <t>RMD0004723</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -203,6 +203,12 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005813</t>
+  </si>
+  <si>
     <t>Glenn Dalgliesh</t>
   </si>
   <si>
@@ -221,13 +227,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
+    <t>RMD0004139</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -243,34 +243,48 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>800-709-6314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009352</t>
+  </si>
+  <si>
     <t>Financial</t>
   </si>
   <si>
     <t>800-7096314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>800-709-6314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -278,21 +292,7 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009020</t>
@@ -335,7 +335,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -349,6 +349,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -366,12 +372,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0006774</t>
@@ -437,7 +437,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005819</t>
+    <t>RMD0004724</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -447,16 +447,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005819</t>
+  </si>
+  <si>
     <t>4109121000</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004724</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004849</t>
@@ -521,10 +521,33 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -558,29 +581,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0002900</t>
   </si>
   <si>
@@ -631,7 +631,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004110</t>
+    <t>RMD0004738</t>
   </si>
   <si>
     <t>RyTel, LLC</t>
@@ -642,12 +642,6 @@
 Salt Lake City UT 84119</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004738</t>
-  </si>
-  <si>
     <t>Lamont Snarr</t>
   </si>
   <si>
@@ -665,6 +659,12 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9650dd421bcd38102eb2a82fe54bcb46&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005124</t>
@@ -861,7 +861,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=47035e5e1b7eb4109ac2ea04bc4bcbb1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004404</t>
+    <t>RMD0009817</t>
   </si>
   <si>
     <t>Call Bound LLC</t>
@@ -871,25 +871,25 @@
 Miami FL 33131</t>
   </si>
   <si>
+    <t>Sze Dai Wei</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>'+1 305 705-7873</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e2dcbec51bd54510e4ec848ce54bcb81&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004404</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=a73e1eb11b49f41064c4426de54bcb85&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009817</t>
-  </si>
-  <si>
-    <t>Sze Dai Wei</t>
-  </si>
-  <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>'+1 305 705-7873</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e2dcbec51bd54510e4ec848ce54bcb81&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -899,6 +899,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -915,12 +921,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005461</t>
@@ -1102,7 +1102,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9277fe1b7a3810dcd1ed3be54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
+    <t>RMD0007575</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1115,13 +1115,13 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007626</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007575</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007716</t>
@@ -1174,7 +1174,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008097</t>
+    <t>RMD0008064</t>
   </si>
   <si>
     <t>Sam Asher Computing Services, Inc.</t>
@@ -1189,6 +1189,12 @@
 Hyper-Reach</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008097</t>
+  </si>
+  <si>
     <t>Caitlin Olfano</t>
   </si>
   <si>
@@ -1201,13 +1207,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4172e7f21b7a3810dcd1ed3be54bcbb5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008064</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
+    <t>RMD0008393</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1215,6 +1215,12 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1232,13 +1238,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008393</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
+    <t>RMD0008451</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1248,16 +1248,16 @@
 Greensboro NC 27401</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008450</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008610</t>
+    <t>RMD0008611</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1270,31 +1270,31 @@
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008756</t>
@@ -1322,7 +1322,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1335,58 +1335,58 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+    <t>RMD0008787</t>
+  </si>
+  <si>
+    <t>Personal Computers Plus</t>
+  </si>
+  <si>
+    <t>0031485048</t>
+  </si>
+  <si>
+    <t>Jeffrey Houston</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>'+16039294272</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008786</t>
   </si>
   <si>
-    <t>Personal Computers Plus</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008787</t>
-  </si>
-  <si>
-    <t>0031485048</t>
-  </si>
-  <si>
-    <t>Jeffrey Houston</t>
-  </si>
-  <si>
-    <t>Networking</t>
-  </si>
-  <si>
-    <t>'+16039294272</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1396,16 +1396,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -1440,7 +1440,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=af63c18f1b3bb010c8e0ed3ce54bcb41&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009728</t>
+    <t>RMD0009729</t>
   </si>
   <si>
     <t>Huffman Telcom Corp</t>
@@ -1450,22 +1450,22 @@
 Fort Collins CO 80524</t>
   </si>
   <si>
+    <t>Charlie Huffman</t>
+  </si>
+  <si>
+    <t>Customer Services</t>
+  </si>
+  <si>
+    <t>'+13033140978</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009728</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=a48d8f371bac051085edebdbac4bcbba&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009729</t>
-  </si>
-  <si>
-    <t>Charlie Huffman</t>
-  </si>
-  <si>
-    <t>Customer Services</t>
-  </si>
-  <si>
-    <t>'+13033140978</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0011742</t>
@@ -6052,28 +6052,14 @@
         <v>59</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
         <v>29</v>
       </c>
@@ -6081,16 +6067,16 @@
         <v>29</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1">
         <v>17118795</v>
@@ -6114,14 +6100,28 @@
         <v>59</v>
       </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="R8" s="1" t="s">
         <v>29</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>29</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1" t="s">
@@ -6155,15 +6155,9 @@
       <c r="F9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
         <v>71</v>
       </c>
@@ -6221,9 +6215,15 @@
       <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="1" t="s">
         <v>71</v>
       </c>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>26</v>
@@ -6456,7 +6456,7 @@
         <v>100</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>26</v>
@@ -6486,55 +6486,41 @@
         <v>104</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
         <v>105</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U15" s="1"/>
       <c r="V15" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B16" s="1">
         <v>23003460</v>
@@ -6546,32 +6532,46 @@
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
         <v>105</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R16" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
@@ -6800,28 +6800,14 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1" t="s">
         <v>29</v>
       </c>
@@ -6829,16 +6815,16 @@
         <v>29</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U21" s="1"/>
       <c r="V21" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B22" s="1">
         <v>25462672</v>
@@ -6858,14 +6844,28 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="R22" s="1" t="s">
         <v>29</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>29</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1" t="s">
@@ -7105,40 +7105,34 @@
       <c r="L27" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B28" s="1">
         <v>27710730</v>
@@ -7147,7 +7141,7 @@
         <v>161</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>29</v>
@@ -7159,35 +7153,41 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="N28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U28" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U28" s="1"/>
       <c r="V28" s="1" t="s">
         <v>177</v>
       </c>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>26</v>
@@ -7336,31 +7336,47 @@
       <c r="I31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R31" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U31" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="V31" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1">
         <v>28073088</v>
@@ -7386,40 +7402,24 @@
       <c r="I32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>201</v>
-      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U32" s="1"/>
       <c r="V32" s="1" t="s">
         <v>203</v>
       </c>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>26</v>
@@ -7998,31 +7998,45 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R43" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1">
         <v>31095391</v>
@@ -8042,36 +8056,22 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8099,48 +8099,32 @@
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>279</v>
-      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B46" s="1">
         <v>31124688</v>
@@ -8159,23 +8143,39 @@
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>281</v>
+      </c>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
+      <c r="Q46" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="R46" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="P48" s="1"/>
       <c r="Q48" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>29</v>
@@ -8713,7 +8713,7 @@
         <v>337</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="Q56" s="1" t="s">
         <v>52</v>
@@ -9032,55 +9032,41 @@
         <v>364</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>365</v>
       </c>
       <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>368</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="Q63" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:22">
       <c r="A64" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B64" s="1">
         <v>31447154</v>
@@ -9092,32 +9078,46 @@
         <v>364</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
         <v>365</v>
       </c>
       <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
+      <c r="J64" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
+      <c r="Q64" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R64" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1" t="s">
@@ -9146,43 +9146,31 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-      <c r="J65" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>336</v>
-      </c>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
-      <c r="M65" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>377</v>
-      </c>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
       <c r="P65" s="1"/>
-      <c r="Q65" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" spans="1:22">
       <c r="A66" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B66" s="1">
         <v>31455868</v>
@@ -9202,22 +9190,34 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>336</v>
+      </c>
       <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
+      <c r="M66" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>379</v>
+      </c>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
+      <c r="Q66" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R66" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
@@ -9333,7 +9333,9 @@
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
+      <c r="I69" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -9353,12 +9355,12 @@
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B70" s="1">
         <v>31475270</v>
@@ -9373,38 +9375,50 @@
         <v>26</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
+      <c r="Q70" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R70" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B71" s="1">
         <v>31475270</v>
@@ -9419,41 +9433,27 @@
         <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-      <c r="J71" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>398</v>
-      </c>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q71" s="1"/>
       <c r="R71" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U71" s="1"/>
       <c r="V71" s="1" t="s">
@@ -9542,7 +9542,7 @@
         <v>406</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>26</v>
@@ -9572,41 +9572,57 @@
         <v>410</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
         <v>411</v>
       </c>
       <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="R74" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B75" s="1">
         <v>31489362</v>
@@ -9618,48 +9634,32 @@
         <v>410</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
         <v>411</v>
       </c>
       <c r="I75" s="1"/>
-      <c r="J75" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U75" s="1"/>
       <c r="V75" s="1" t="s">
@@ -9680,39 +9680,59 @@
         <v>401</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>422</v>
+      </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R76" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U76" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="V76" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B77" s="1">
         <v>31491517</v>
@@ -9724,52 +9744,32 @@
         <v>401</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>424</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="P77" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U77" s="1" t="s">
-        <v>214</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U77" s="1"/>
       <c r="V77" s="1" t="s">
         <v>428</v>
       </c>
@@ -9788,49 +9788,39 @@
         <v>431</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="1" t="s">
-        <v>430</v>
-      </c>
+      <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-      <c r="M78" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>432</v>
-      </c>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
       <c r="P78" s="1"/>
-      <c r="Q78" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U78" s="1"/>
       <c r="V78" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="79" spans="1:22">
       <c r="A79" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B79" s="1">
         <v>31544182</v>
@@ -9842,30 +9832,40 @@
         <v>431</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>430</v>
+      </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
+      <c r="M79" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>434</v>
+      </c>
       <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
+      <c r="Q79" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R79" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U79" s="1"/>
       <c r="V79" s="1" t="s">
@@ -9988,39 +9988,53 @@
         <v>448</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
+      <c r="J82" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
+      <c r="Q82" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R82" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U82" s="1"/>
       <c r="V82" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B83" s="1">
         <v>31758865</v>
@@ -10032,44 +10046,30 @@
         <v>448</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>453</v>
-      </c>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
       <c r="P83" s="1"/>
-      <c r="Q83" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q83" s="1"/>
       <c r="R83" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1" t="s">
@@ -10232,7 +10232,7 @@
         <v>475</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>29</v>
@@ -10412,7 +10412,7 @@
         <v>498</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>29</v>
@@ -10658,7 +10658,7 @@
         <v>524</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>50</v>
@@ -10931,7 +10931,7 @@
         <v>294</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M99" s="1" t="s">
         <v>546</v>
@@ -11619,7 +11619,7 @@
         <v>72</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>615</v>
@@ -11897,7 +11897,7 @@
         <v>26</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
@@ -11915,7 +11915,7 @@
         <v>651</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O116" s="1" t="s">
         <v>652</v>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>26</v>
@@ -12193,7 +12193,7 @@
         <v>72</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>682</v>
@@ -12289,7 +12289,7 @@
         <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
@@ -13101,7 +13101,7 @@
         <v>26</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>43</v>
@@ -13125,7 +13125,7 @@
         <v>778</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>781</v>
@@ -13161,7 +13161,7 @@
         <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
@@ -13170,7 +13170,7 @@
         <v>784</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>146</v>
@@ -13179,7 +13179,7 @@
         <v>785</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O139" s="1" t="s">
         <v>786</v>
@@ -13367,7 +13367,7 @@
         <v>294</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>804</v>
@@ -13509,7 +13509,7 @@
         <v>26</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>43</v>
@@ -13555,7 +13555,7 @@
         <v>26</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -13831,7 +13831,7 @@
         <v>294</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>844</v>
@@ -14039,7 +14039,7 @@
         <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>43</v>
@@ -14063,14 +14063,14 @@
         <v>867</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>868</v>
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>26</v>
@@ -14160,7 +14160,7 @@
         <v>879</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>50</v>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>26</v>
@@ -14775,7 +14775,7 @@
         <v>939</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
@@ -15046,7 +15046,7 @@
         <v>967</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L175" s="1" t="s">
         <v>98</v>
@@ -15103,7 +15103,7 @@
         <v>972</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="1" t="s">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>26</v>
@@ -15156,7 +15156,7 @@
         <v>979</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L177" s="1" t="s">
         <v>980</v>
@@ -15259,7 +15259,7 @@
         <v>26</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>26</v>
@@ -15437,7 +15437,7 @@
         <v>294</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M182" s="1" t="s">
         <v>1007</v>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>26</v>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="P183" s="1"/>
       <c r="Q183" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>29</v>
@@ -15629,7 +15629,7 @@
         <v>26</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
@@ -15645,14 +15645,14 @@
       </c>
       <c r="M186" s="1"/>
       <c r="N186" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O186" s="1" t="s">
         <v>1028</v>
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>26</v>
@@ -15809,7 +15809,7 @@
         <v>72</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M189" s="1"/>
       <c r="N189" s="1" t="s">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>26</v>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="P195" s="1"/>
       <c r="Q195" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R195" s="1" t="s">
         <v>26</v>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>26</v>
@@ -16598,7 +16598,7 @@
         <v>1138</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L203" s="1" t="s">
         <v>72</v>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="P205" s="1"/>
       <c r="Q205" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>26</v>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>26</v>
@@ -17168,10 +17168,10 @@
         <v>1200</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>1201</v>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>26</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>26</v>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -17941,7 +17941,7 @@
         <v>972</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>1282</v>
@@ -18001,7 +18001,7 @@
         <v>972</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>1288</v>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>26</v>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>26</v>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>26</v>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>26</v>
@@ -18496,10 +18496,10 @@
         <v>1345</v>
       </c>
       <c r="K235" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M235" s="1" t="s">
         <v>1346</v>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>26</v>
@@ -18562,7 +18562,7 @@
         <v>1353</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>221</v>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>26</v>
@@ -18758,7 +18758,7 @@
         <v>1378</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L239" s="1" t="s">
         <v>1379</v>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>26</v>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="P242" s="1"/>
       <c r="Q242" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R242" s="1" t="s">
         <v>26</v>
@@ -19133,7 +19133,7 @@
         <v>1415</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1420</v>
@@ -19190,7 +19190,7 @@
         <v>1426</v>
       </c>
       <c r="K246" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L246" s="1" t="s">
         <v>482</v>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="P246" s="1"/>
       <c r="Q246" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R246" s="1" t="s">
         <v>29</v>
@@ -19516,7 +19516,7 @@
         <v>1460</v>
       </c>
       <c r="Q251" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>26</v>
@@ -19925,7 +19925,7 @@
         <v>1508</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1504</v>
@@ -19987,7 +19987,7 @@
         <v>1508</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1514</v>
@@ -20047,7 +20047,7 @@
         <v>624</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1522</v>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>26</v>
@@ -20478,10 +20478,10 @@
         <v>1567</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1565</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="P267" s="1"/>
       <c r="Q267" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R267" s="1" t="s">
         <v>26</v>
@@ -20688,7 +20688,7 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>26</v>
@@ -20798,7 +20798,7 @@
         <v>1605</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L272" s="1" t="s">
         <v>190</v>
@@ -20814,7 +20814,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>26</v>
@@ -20858,7 +20858,7 @@
         <v>1605</v>
       </c>
       <c r="K273" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L273" s="1" t="s">
         <v>190</v>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>26</v>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>26</v>
@@ -21174,7 +21174,7 @@
         <v>1652</v>
       </c>
       <c r="Q278" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>26</v>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>26</v>
@@ -21298,7 +21298,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>26</v>
